--- a/SSL certificates list Prod_test.xlsx
+++ b/SSL certificates list Prod_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\manoj.sai.ghanta\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F7D4284-F91B-4001-8081-331F7A581304}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCEEB1B1-0BE0-46C4-88C4-2DB16FA5839D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{97F08258-8752-4997-929A-F4F213A389E7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
   <si>
     <t>Kurzbeschreibung</t>
   </si>
@@ -50,9 +50,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Certs</t>
-  </si>
-  <si>
     <t>Prod</t>
   </si>
   <si>
@@ -131,6 +128,81 @@
     <t>myWizard-ta.pem(multichain); myWizard-ta.key</t>
   </si>
   <si>
+    <t>Dev</t>
+  </si>
+  <si>
+    <t>myWizardDS-ATR.telekom.de</t>
+  </si>
+  <si>
+    <t>10.103.108.133</t>
+  </si>
+  <si>
+    <t>Telekom Security ServerID OV Class 2 CA - 29114F516CE902CEAE0DA578C804B9F3</t>
+  </si>
+  <si>
+    <t>myWizardDS-ATR.crt(multichain certificate), myWizardDS-ATR.key</t>
+  </si>
+  <si>
+    <t>myWizardDS-Automation.telekom.de</t>
+  </si>
+  <si>
+    <t>10.103.108.136</t>
+  </si>
+  <si>
+    <t>Telekom Security ServerID OV Class 2 CA - 29C9D5AF7C2317999FCF6E20660750</t>
+  </si>
+  <si>
+    <t>mywizardDS-Automation_16072024.cer; myWizardDS-Automation.telekom.de.crt</t>
+  </si>
+  <si>
+    <t>myWizardDS-PAM.telekom.de</t>
+  </si>
+  <si>
+    <t>10.103.108.134</t>
+  </si>
+  <si>
+    <t>Telekom Security ServerID OV Class 2 CA - 2854934FF6810718219478B832A6EF27</t>
+  </si>
+  <si>
+    <t>myWizardDS-pam.key , myWizardDS-pam_Server.ID-322813-x509chain.pem</t>
+  </si>
+  <si>
+    <t>myWizardDS-RD.telekom.de</t>
+  </si>
+  <si>
+    <t>10.103.108.138</t>
+  </si>
+  <si>
+    <t>Telekom Security ServerID OV Class 2 CA - 3188B24F6745E8035F0EDD27D8FC97CE</t>
+  </si>
+  <si>
+    <t>myWizardDS-rd.key , myWizardDSrd_Server.ID-322813-x509chain.pem</t>
+  </si>
+  <si>
+    <t>myWizardDS-SI.telekom.de</t>
+  </si>
+  <si>
+    <t>10.103.108.143</t>
+  </si>
+  <si>
+    <t>Telekom Security ServerID OV Class 2 CA - 338576E73D3789EEBD219A0FA4E13492</t>
+  </si>
+  <si>
+    <t>mywizardDS-si.telekom.de-chain.crt (multi chain certificate); myWizardDS_si.key</t>
+  </si>
+  <si>
+    <t>myWizardDS-TA.telekom.de</t>
+  </si>
+  <si>
+    <t>10.103.108.135</t>
+  </si>
+  <si>
+    <t>Telekom Security ServerID OV Class 2 CA - 3F66D307EA96689DFA04B6017096EE7B</t>
+  </si>
+  <si>
+    <t>myWizardDS-ta.pem(multichain); myWizardDS-ta.key</t>
+  </si>
+  <si>
     <t>Test</t>
   </si>
   <si>
@@ -198,6 +270,12 @@
   </si>
   <si>
     <t>Environment</t>
+  </si>
+  <si>
+    <t>Requried Certs</t>
+  </si>
+  <si>
+    <t>myWizard(DEV)</t>
   </si>
 </sst>
 </file>
@@ -255,7 +333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -270,6 +348,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -606,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{766F14F8-2B40-4EFD-9950-90CB70C3BD75}">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="12.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7265625" customWidth="1"/>
@@ -619,7 +706,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -634,127 +721,127 @@
         <v>3</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>4</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="6" t="s">
         <v>13</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" t="s">
         <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="6" t="s">
         <v>25</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" t="s">
         <v>29</v>
-      </c>
-      <c r="F7" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
@@ -773,105 +860,225 @@
     </row>
     <row r="10" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="12.5" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="1:6" s="8" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C16" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="8" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="8" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="8" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="8" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="F20" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="3" t="s">
+    </row>
+    <row r="21" spans="1:6" s="8" customFormat="1" ht="12.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F14" t="s">
+      <c r="C21" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D21" s="9" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="12.5" x14ac:dyDescent="0.25"/>
+      <c r="E21" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="1" gridLinesSet="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
